--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6347" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6347" uniqueCount="694">
   <si>
     <t>Property</t>
   </si>
@@ -812,9 +812,6 @@
     <t>Observation.extension:bodyStructure.extension</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Observation.extension:bodyStructure.extension:structure</t>
   </si>
   <si>
@@ -1016,9 +1013,6 @@
   </si>
   <si>
     <t>qualifier</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>【JP Core仕様】特定の歯の歯根と、歯面の２項目を指定</t>
@@ -1195,6 +1189,9 @@
   </si>
   <si>
     <t>Observation.category</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Observationの種類（タイプ）の分類
@@ -5789,7 +5786,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>82</v>
@@ -5896,13 +5893,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>83</v>
@@ -5927,10 +5924,10 @@
         <v>139</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6016,10 +6013,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6134,10 +6131,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6252,10 +6249,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6295,7 +6292,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>83</v>
@@ -6372,10 +6369,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6431,11 +6428,11 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6488,13 +6485,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
@@ -6608,10 +6605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6726,10 +6723,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6844,10 +6841,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6887,7 +6884,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6964,10 +6961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7082,13 +7079,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>83</v>
@@ -7202,10 +7199,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7320,10 +7317,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7440,13 +7437,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>83</v>
@@ -7560,10 +7557,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7678,10 +7675,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7796,10 +7793,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7839,7 +7836,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7916,10 +7913,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8034,13 +8031,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>83</v>
@@ -8154,10 +8151,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8272,10 +8269,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8390,10 +8387,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8433,7 +8430,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>83</v>
@@ -8510,10 +8507,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8628,13 +8625,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>83</v>
@@ -8748,10 +8745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8866,10 +8863,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8984,13 +8981,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>83</v>
@@ -9104,10 +9101,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9222,10 +9219,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9340,10 +9337,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9383,7 +9380,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9460,10 +9457,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B59" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9486,7 +9483,7 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>172</v>
@@ -9578,10 +9575,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9621,7 +9618,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9698,10 +9695,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9724,7 +9721,7 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>172</v>
@@ -9816,13 +9813,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>83</v>
@@ -9936,10 +9933,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10054,10 +10051,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10172,10 +10169,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10215,7 +10212,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>83</v>
@@ -10292,10 +10289,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10410,10 +10407,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10453,7 +10450,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>83</v>
@@ -10530,10 +10527,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10556,7 +10553,7 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -10648,20 +10645,20 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>82</v>
@@ -10679,10 +10676,10 @@
         <v>139</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10768,10 +10765,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10886,10 +10883,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11004,10 +11001,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11047,7 +11044,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>83</v>
@@ -11124,10 +11121,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11242,20 +11239,20 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>94</v>
@@ -11362,20 +11359,20 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
@@ -11482,7 +11479,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>163</v>
@@ -11525,7 +11522,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>83</v>
@@ -11602,7 +11599,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>170</v>
@@ -11628,7 +11625,7 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>172</v>
@@ -11720,10 +11717,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11749,16 +11746,16 @@
         <v>139</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11807,7 +11804,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11842,10 +11839,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11868,19 +11865,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11929,7 +11926,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11944,19 +11941,19 @@
         <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -11964,14 +11961,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11990,19 +11987,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12051,7 +12048,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12066,16 +12063,16 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12086,14 +12083,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12112,16 +12109,16 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12171,7 +12168,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12186,16 +12183,16 @@
         <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12206,10 +12203,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12235,16 +12232,16 @@
         <v>114</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O82" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12269,13 +12266,13 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12293,7 +12290,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>94</v>
@@ -12308,19 +12305,19 @@
         <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12328,10 +12325,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12339,7 +12336,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>258</v>
+        <v>380</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>82</v>
@@ -12357,16 +12354,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12394,16 +12391,16 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB83" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
@@ -12413,7 +12410,7 @@
         <v>143</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12437,10 +12434,10 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12448,13 +12445,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>83</v>
@@ -12479,16 +12476,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12513,11 +12510,11 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12535,7 +12532,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12559,10 +12556,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12570,10 +12567,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12688,10 +12685,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12808,10 +12805,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12930,10 +12927,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13048,10 +13045,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13168,10 +13165,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13213,7 +13210,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>83</v>
@@ -13290,10 +13287,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13410,10 +13407,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13453,7 +13450,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>83</v>
@@ -13530,10 +13527,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13650,10 +13647,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13772,10 +13769,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13894,13 +13891,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -13925,16 +13922,16 @@
         <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N96" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13962,11 +13959,11 @@
         <v>118</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>386</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13983,7 +13980,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14007,10 +14004,10 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14018,10 +14015,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14136,10 +14133,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14256,10 +14253,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14378,10 +14375,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14496,10 +14493,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14616,10 +14613,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14661,7 +14658,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>83</v>
@@ -14738,10 +14735,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14858,10 +14855,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14901,7 +14898,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>83</v>
@@ -14978,10 +14975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15098,10 +15095,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15220,10 +15217,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15342,13 +15339,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>83</v>
@@ -15373,16 +15370,16 @@
         <v>171</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N108" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O108" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15407,11 +15404,11 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15429,7 +15426,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15453,10 +15450,10 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -15464,10 +15461,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15582,10 +15579,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15702,10 +15699,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15824,10 +15821,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15942,10 +15939,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16062,10 +16059,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16107,7 +16104,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16184,10 +16181,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16304,10 +16301,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16347,7 +16344,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>83</v>
@@ -16424,10 +16421,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16544,10 +16541,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16666,10 +16663,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16788,14 +16785,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16817,16 +16814,16 @@
         <v>171</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M120" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>83</v>
@@ -16851,14 +16848,14 @@
         <v>83</v>
       </c>
       <c r="X120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Y120" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Y120" t="s" s="2">
+      <c r="Z120" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
       </c>
@@ -16875,7 +16872,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>94</v>
@@ -16890,30 +16887,30 @@
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL120" t="s" s="2">
+      <c r="AM120" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM120" t="s" s="2">
+      <c r="AN120" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AN120" t="s" s="2">
+      <c r="AO120" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AO120" t="s" s="2">
+      <c r="AP120" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17028,10 +17025,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17148,10 +17145,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17177,10 +17174,10 @@
         <v>186</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>189</v>
@@ -17270,10 +17267,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17388,10 +17385,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17508,10 +17505,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17553,7 +17550,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>83</v>
@@ -17630,10 +17627,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17750,10 +17747,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17793,7 +17790,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>83</v>
@@ -17870,10 +17867,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17916,7 +17913,7 @@
         <v>83</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>83</v>
@@ -17990,10 +17987,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18112,10 +18109,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18234,10 +18231,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18260,19 +18257,19 @@
         <v>95</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M132" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -18321,7 +18318,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -18336,19 +18333,19 @@
         <v>106</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM132" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM132" t="s" s="2">
+      <c r="AN132" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AN132" t="s" s="2">
+      <c r="AO132" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
@@ -18356,10 +18353,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18382,16 +18379,16 @@
         <v>95</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18441,7 +18438,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18462,13 +18459,13 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>
@@ -18476,14 +18473,14 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18502,19 +18499,19 @@
         <v>95</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M134" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>83</v>
@@ -18563,7 +18560,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -18578,19 +18575,19 @@
         <v>106</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AL134" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM134" t="s" s="2">
+      <c r="AN134" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AN134" t="s" s="2">
+      <c r="AO134" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>83</v>
@@ -18598,14 +18595,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18624,19 +18621,19 @@
         <v>95</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M135" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>83</v>
@@ -18685,7 +18682,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18700,19 +18697,19 @@
         <v>106</v>
       </c>
       <c r="AK135" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AL135" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM135" t="s" s="2">
+      <c r="AN135" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AN135" t="s" s="2">
+      <c r="AO135" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>83</v>
@@ -18720,10 +18717,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18746,16 +18743,16 @@
         <v>95</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18805,7 +18802,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -18826,13 +18823,13 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN136" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AN136" t="s" s="2">
+      <c r="AO136" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>
@@ -18840,10 +18837,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18866,19 +18863,19 @@
         <v>95</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M137" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -18927,7 +18924,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -18942,19 +18939,19 @@
         <v>106</v>
       </c>
       <c r="AK137" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AL137" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM137" t="s" s="2">
+      <c r="AN137" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN137" t="s" s="2">
+      <c r="AO137" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>83</v>
@@ -18962,10 +18959,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18991,16 +18988,16 @@
         <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M138" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
@@ -19049,7 +19046,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19058,7 +19055,7 @@
         <v>94</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>106</v>
@@ -19067,27 +19064,27 @@
         <v>83</v>
       </c>
       <c r="AL138" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AM138" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM138" t="s" s="2">
+      <c r="AN138" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP138" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>537</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19113,16 +19110,16 @@
         <v>171</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M139" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>83</v>
@@ -19147,40 +19144,40 @@
         <v>83</v>
       </c>
       <c r="X139" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="Y139" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="Y139" t="s" s="2">
+      <c r="Z139" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z139" t="s" s="2">
+      <c r="AA139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI139" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>106</v>
@@ -19195,7 +19192,7 @@
         <v>137</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
@@ -19206,14 +19203,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -19235,16 +19232,16 @@
         <v>171</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N140" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19269,14 +19266,14 @@
         <v>83</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y140" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z140" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z140" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
       </c>
@@ -19293,7 +19290,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19311,27 +19308,27 @@
         <v>83</v>
       </c>
       <c r="AL140" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM140" t="s" s="2">
+      <c r="AN140" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN140" t="s" s="2">
+      <c r="AO140" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP140" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19354,19 +19351,19 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M141" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>83</v>
@@ -19415,7 +19412,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19436,10 +19433,10 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
@@ -19450,10 +19447,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19479,13 +19476,13 @@
         <v>171</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19511,14 +19508,14 @@
         <v>83</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y142" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z142" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="Z142" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="AA142" t="s" s="2">
         <v>83</v>
       </c>
@@ -19535,7 +19532,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19553,27 +19550,27 @@
         <v>83</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM142" t="s" s="2">
+      <c r="AN142" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AN142" t="s" s="2">
+      <c r="AO142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP142" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19599,16 +19596,16 @@
         <v>171</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="M143" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19633,14 +19630,14 @@
         <v>83</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="Z143" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="AA143" t="s" s="2">
         <v>83</v>
       </c>
@@ -19657,7 +19654,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19678,10 +19675,10 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN143" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19692,10 +19689,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19718,16 +19715,16 @@
         <v>83</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L144" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L144" t="s" s="2">
+      <c r="M144" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19777,7 +19774,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19795,27 +19792,27 @@
         <v>83</v>
       </c>
       <c r="AL144" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM144" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM144" t="s" s="2">
+      <c r="AN144" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AN144" t="s" s="2">
+      <c r="AO144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP144" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP144" t="s" s="2">
-        <v>589</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19838,16 +19835,16 @@
         <v>83</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19897,7 +19894,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -19915,27 +19912,27 @@
         <v>83</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM145" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM145" t="s" s="2">
+      <c r="AN145" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="AN145" t="s" s="2">
+      <c r="AO145" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP145" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP145" t="s" s="2">
-        <v>597</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19946,7 +19943,7 @@
         <v>81</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>83</v>
@@ -19958,19 +19955,19 @@
         <v>83</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M146" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>83</v>
@@ -20019,7 +20016,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20031,19 +20028,19 @@
         <v>83</v>
       </c>
       <c r="AJ146" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM146" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AK146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM146" t="s" s="2">
+      <c r="AN146" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>83</v>
@@ -20054,10 +20051,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20172,10 +20169,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20292,14 +20289,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20321,16 +20318,16 @@
         <v>139</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20379,7 +20376,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20414,10 +20411,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20440,13 +20437,13 @@
         <v>83</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20497,7 +20494,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20506,7 +20503,7 @@
         <v>94</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
@@ -20518,10 +20515,10 @@
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN150" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
@@ -20532,10 +20529,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20558,13 +20555,13 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20615,7 +20612,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20624,7 +20621,7 @@
         <v>94</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>106</v>
@@ -20636,10 +20633,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20650,10 +20647,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20679,16 +20676,16 @@
         <v>171</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="N152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
@@ -20716,11 +20713,11 @@
         <v>118</v>
       </c>
       <c r="Y152" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="Z152" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="Z152" t="s" s="2">
-        <v>630</v>
-      </c>
       <c r="AA152" t="s" s="2">
         <v>83</v>
       </c>
@@ -20737,7 +20734,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20755,13 +20752,13 @@
         <v>83</v>
       </c>
       <c r="AL152" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AM152" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AN152" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -20772,10 +20769,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20801,16 +20798,16 @@
         <v>171</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>83</v>
@@ -20835,14 +20832,14 @@
         <v>83</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="Z153" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>639</v>
-      </c>
       <c r="AA153" t="s" s="2">
         <v>83</v>
       </c>
@@ -20859,7 +20856,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -20877,13 +20874,13 @@
         <v>83</v>
       </c>
       <c r="AL153" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AM153" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AN153" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -20894,10 +20891,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20920,17 +20917,17 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>83</v>
@@ -20979,7 +20976,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21003,7 +21000,7 @@
         <v>83</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21014,10 +21011,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21043,10 +21040,10 @@
         <v>153</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21097,7 +21094,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21118,10 +21115,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21132,10 +21129,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21158,16 +21155,16 @@
         <v>95</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21217,7 +21214,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21238,10 +21235,10 @@
         <v>83</v>
       </c>
       <c r="AM156" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN156" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
@@ -21252,10 +21249,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21278,16 +21275,16 @@
         <v>95</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21337,7 +21334,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21358,10 +21355,10 @@
         <v>83</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21372,10 +21369,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21398,19 +21395,19 @@
         <v>95</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M158" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>83</v>
@@ -21459,7 +21456,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21480,10 +21477,10 @@
         <v>83</v>
       </c>
       <c r="AM158" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN158" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
@@ -21494,10 +21491,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21612,10 +21609,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21732,14 +21729,14 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -21761,16 +21758,16 @@
         <v>139</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -21819,7 +21816,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -21854,10 +21851,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21883,16 +21880,16 @@
         <v>171</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N162" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O162" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -21917,14 +21914,14 @@
         <v>83</v>
       </c>
       <c r="X162" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Y162" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Y162" t="s" s="2">
+      <c r="Z162" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z162" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
       </c>
@@ -21941,7 +21938,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>94</v>
@@ -21959,16 +21956,16 @@
         <v>83</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AM162" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN162" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AN162" t="s" s="2">
+      <c r="AO162" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AO162" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>83</v>
@@ -21976,10 +21973,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22002,19 +21999,19 @@
         <v>95</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="N163" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="O163" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22063,7 +22060,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22081,27 +22078,27 @@
         <v>83</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AM163" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO163" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP163" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP163" t="s" s="2">
-        <v>537</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22127,16 +22124,16 @@
         <v>171</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="N164" t="s" s="2">
-        <v>684</v>
-      </c>
       <c r="O164" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -22161,40 +22158,40 @@
         <v>83</v>
       </c>
       <c r="X164" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="Y164" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="Y164" t="s" s="2">
+      <c r="Z164" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z164" t="s" s="2">
+      <c r="AA164" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI164" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH164" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI164" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>106</v>
@@ -22209,7 +22206,7 @@
         <v>137</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>83</v>
@@ -22220,14 +22217,14 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -22249,16 +22246,16 @@
         <v>171</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>83</v>
@@ -22283,14 +22280,14 @@
         <v>83</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y165" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z165" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z165" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
       </c>
@@ -22307,7 +22304,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22325,27 +22322,27 @@
         <v>83</v>
       </c>
       <c r="AL165" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM165" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM165" t="s" s="2">
+      <c r="AN165" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN165" t="s" s="2">
+      <c r="AO165" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP165" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP165" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22371,16 +22368,16 @@
         <v>84</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>83</v>
@@ -22429,7 +22426,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22450,10 +22447,10 @@
         <v>83</v>
       </c>
       <c r="AM166" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6347" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6717" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -1036,10 +1036,53 @@
     <t>qualifier/root</t>
   </si>
   <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_VS</t>
+  </si>
+  <si>
     <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface</t>
   </si>
   <si>
     <t>qualifier/surface</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_VS</t>
   </si>
   <si>
     <t>Observation.extension:bodyStructure.url</t>
@@ -1075,8 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>Observationのためのビジネス識別子  
-【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
+    <t>Observationのためのビジネス識別子 【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
   </si>
   <si>
     <t>例：実施日に連番を付加した番号</t>
@@ -1108,8 +1150,7 @@
 </t>
   </si>
   <si>
-    <t>実施されるプラン、提案、依頼  
-【JP Core仕様】未使用</t>
+    <t>実施されるプラン、提案、依頼  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>本プロファイル（複数の部位が同一の疾患を有していたり、複数部位からなる疾患が存在した際に、複数の部位を表現することのできるプロファイル）は診療情報提供書に紐付く前提のため、本プロファイル特有の定義はしない。</t>
@@ -1138,8 +1179,7 @@
 </t>
   </si>
   <si>
-    <t>参照されるイベントの一部分
-【JP Core仕様】未使用</t>
+    <t>参照されるイベントの一部分 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
@@ -1157,8 +1197,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態  
-【JP Core仕様】ステータス</t>
+    <t>結果の状態 【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -1194,14 +1233,14 @@
     <t>3</t>
   </si>
   <si>
-    <t>Observationの種類（タイプ）の分類
-【JP Core仕様】以下を指定する。
-第1コード：exam
-第2コード：LP89803-8（Dental）
+    <t>Observationの種類（タイプ）の分類 【JP Core仕様】各種Catageoryは固定となる</t>
+  </si>
+  <si>
+    <t>このObservationの分類。  
+【JP Core仕様】以下を指定する。  
+第1コード：exam  
+第2コード：LP89803-8（Dental）  
 第3コード：DO-1-04（ClinicalInformationSharing）</t>
-  </si>
-  <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
@@ -1319,6 +1358,9 @@
     <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
   </si>
   <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -1461,8 +1503,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>observation のタイプ（コードまたはタイプ）
-【JP Core仕様】57133-1（Referral note）を指定する</t>
+    <t>observation のタイプ（コードまたはタイプ 【JP Core仕様】57133-1（Referral note）を指定する</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
@@ -1502,8 +1543,7 @@
 </t>
   </si>
   <si>
-    <t>観察対象者  
-【JP Core仕様】患者情報</t>
+    <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
     <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
@@ -1531,8 +1571,7 @@
 </t>
   </si>
   <si>
-    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  
-【JP Core仕様】未使用</t>
+    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
@@ -1584,8 +1623,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】実施日時</t>
+    <t>臨床的に関連する時刻または時間 【JP Core仕様】実施日時</t>
   </si>
   <si>
     <t>この観察結果が過去の報告でない限り、少なくとも日付が存在する必要がある。不正確または「あいまいな」時間を記録するには（たとえば、「朝食後」に行われた血糖測定）、[Timing]（datatypes.html＃timing）データ型を使用して、測定を通常のライフイベントに関連付けることができる。</t>
@@ -1613,8 +1651,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが利用可能となった日時  
-【JP Core仕様】所見確定日時</t>
+    <t>このバージョンが利用可能となった日時 JP Core仕様】所見確定日時</t>
   </si>
   <si>
     <t>レビューと検証を必要としないobservationの場合、リソース自体の[`lastUpdated`]（resource-definitions.html＃Meta.lastUpdated）日時と同じになる場合がある。特定の更新のレビューと検証が必要なobservationの場合、新しいバージョンを再度レビューして検証する必要がないような臨床的に重要でない更新がなされたために、リソース自体の「lastUpdated」時間はこれと異なる場合がある。</t>
@@ -1660,8 +1697,7 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>実際の結果値  
-【JP Core仕様】歯の処置状態。現存歯、欠損歯、粒度の細かさ、粗さにかかわらず、そのうち一つをVSより選択する</t>
+    <t>実際の結果値 JP Core仕様】歯の処置状態。現存歯、欠損歯、粒度の細かさ、粗さにかかわらず、そのうち一つをVSより選択する</t>
   </si>
   <si>
     <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1686,8 +1722,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が欠損値である理由
-【JP Core仕様】結果が存在しなかった場合、その理由</t>
+    <t>結果が欠損値である理由 【JP Core仕様】結果が存在しなかった場合、その理由</t>
   </si>
   <si>
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
@@ -1719,8 +1754,7 @@
 </t>
   </si>
   <si>
-    <t>高、低、正常等の結果のカテゴリ分けした評価
-【JP Core仕様】未使用</t>
+    <t>高、低、正常等の結果のカテゴリ分けした評価 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
@@ -1754,8 +1788,7 @@
 </t>
   </si>
   <si>
-    <t>結果に対するコメント  
-【JP Core仕様】未使用</t>
+    <t>結果に対するコメント 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>観察（結果）に関する一般的な記述、重要な、予期しない、または信頼できない結果値に関する記述、またはその解釈に関連する場合はそのソースに関する情報が含まれる場合がある。</t>
@@ -1774,8 +1807,7 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>観察された身体部位  
-【JP Core仕様】未使用</t>
+    <t>観察された身体部位 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
@@ -1832,8 +1864,7 @@
 </t>
   </si>
   <si>
-    <t>観察（観測、検査）に使われた検体材料
-【JP Core仕様】未使用</t>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
@@ -2053,8 +2084,7 @@
 </t>
   </si>
   <si>
-    <t>observationグループに属する関連リソース
-【JP Core仕様】未使用</t>
+    <t>observationグループに属する関連リソース 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいずれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
@@ -2073,8 +2103,7 @@
 </t>
   </si>
   <si>
-    <t>observationの発生源に関連する測定
-【JP Core仕様】未使用</t>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
@@ -2086,8 +2115,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>複合的な結果
-【JP Core仕様】未使用</t>
+    <t>複合的な結果 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -2491,7 +2519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP166"/>
+  <dimension ref="A1:AP176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="108.2890625" customWidth="true" bestFit="true"/>
@@ -11362,11 +11390,9 @@
         <v>332</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11387,13 +11413,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11444,19 +11470,19 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11468,7 +11494,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11479,10 +11505,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>163</v>
+        <v>286</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11490,10 +11516,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11505,24 +11531,22 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>83</v>
@@ -11552,31 +11576,31 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11588,7 +11612,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11599,10 +11623,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>170</v>
+        <v>288</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11610,10 +11634,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11625,15 +11649,17 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>314</v>
+        <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11682,10 +11708,10 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>94</v>
@@ -11694,7 +11720,7 @@
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
@@ -11717,46 +11743,42 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>139</v>
+        <v>314</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>338</v>
+        <v>172</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11792,31 +11814,29 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>341</v>
+        <v>175</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11839,12 +11859,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11853,7 +11875,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11862,23 +11884,19 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>343</v>
+        <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>344</v>
+        <v>172</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11902,13 +11920,11 @@
         <v>83</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>83</v>
@@ -11926,13 +11942,13 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
@@ -11941,19 +11957,19 @@
         <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>349</v>
+        <v>137</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -11961,21 +11977,23 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D80" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -11984,23 +12002,19 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>353</v>
+        <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>354</v>
+        <v>140</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12048,7 +12062,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>351</v>
+        <v>161</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12060,19 +12074,19 @@
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12083,21 +12097,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>361</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
@@ -12106,20 +12120,18 @@
         <v>83</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>362</v>
+        <v>153</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>363</v>
+        <v>154</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12168,31 +12180,31 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>360</v>
+        <v>156</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12203,10 +12215,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>368</v>
+        <v>286</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12214,35 +12226,31 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>369</v>
+        <v>140</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12266,58 +12274,58 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>368</v>
+        <v>161</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12325,10 +12333,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>379</v>
+        <v>344</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>379</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12336,10 +12344,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>380</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12351,20 +12359,18 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>381</v>
+        <v>164</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>381</v>
+        <v>165</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -12388,41 +12394,43 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC83" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12434,10 +12442,10 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12445,23 +12453,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12473,20 +12479,16 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>391</v>
+        <v>172</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12510,35 +12512,35 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>379</v>
+        <v>175</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>83</v>
@@ -12556,10 +12558,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12567,12 +12569,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12593,13 +12597,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12626,13 +12630,11 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12650,7 +12652,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12662,7 +12664,7 @@
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12674,7 +12676,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12685,21 +12687,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>397</v>
+        <v>163</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
@@ -12711,16 +12713,16 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12728,7 +12730,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>83</v>
@@ -12758,31 +12760,31 @@
         <v>83</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12794,7 +12796,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12805,10 +12807,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>399</v>
+        <v>170</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12819,7 +12821,7 @@
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
@@ -12828,23 +12830,19 @@
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>186</v>
+        <v>314</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12892,13 +12890,13 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>83</v>
@@ -12913,10 +12911,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12927,42 +12925,46 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>154</v>
+        <v>352</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
       </c>
@@ -13010,19 +13012,19 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>156</v>
+        <v>355</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13034,7 +13036,7 @@
         <v>83</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13045,14 +13047,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>402</v>
+        <v>356</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13068,21 +13070,23 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>139</v>
+        <v>357</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>182</v>
+        <v>358</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13118,19 +13122,19 @@
         <v>83</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>161</v>
+        <v>356</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13142,22 +13146,22 @@
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>157</v>
+        <v>363</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13165,21 +13169,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -13191,26 +13195,26 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>108</v>
+        <v>367</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>200</v>
+        <v>368</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>201</v>
+        <v>368</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>202</v>
+        <v>369</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>203</v>
+        <v>370</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>406</v>
+        <v>83</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>83</v>
@@ -13252,13 +13256,13 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>205</v>
+        <v>365</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
@@ -13267,16 +13271,16 @@
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>206</v>
+        <v>372</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>207</v>
+        <v>373</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13287,21 +13291,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -13313,16 +13317,16 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>153</v>
+        <v>376</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>211</v>
+        <v>377</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>212</v>
+        <v>378</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13372,13 +13376,13 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>213</v>
+        <v>374</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
@@ -13387,16 +13391,16 @@
         <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>214</v>
+        <v>380</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>215</v>
+        <v>381</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13407,10 +13411,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13427,7 +13431,7 @@
         <v>83</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>95</v>
@@ -13436,21 +13440,23 @@
         <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>218</v>
+        <v>383</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>220</v>
+        <v>385</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>83</v>
@@ -13468,13 +13474,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13492,10 +13498,10 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>221</v>
+        <v>382</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>94</v>
@@ -13507,19 +13513,19 @@
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>222</v>
+        <v>390</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>223</v>
+        <v>391</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13527,10 +13533,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13538,10 +13544,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>81</v>
+        <v>394</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -13550,20 +13556,22 @@
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>226</v>
+        <v>395</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O93" t="s" s="2">
-        <v>228</v>
+        <v>397</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13588,37 +13596,35 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>229</v>
+        <v>393</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
@@ -13633,13 +13639,13 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>230</v>
+        <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>231</v>
+        <v>401</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -13647,21 +13653,23 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13670,22 +13678,22 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>236</v>
+        <v>405</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>237</v>
+        <v>406</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13710,13 +13718,11 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13734,13 +13740,13 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>239</v>
+        <v>393</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
@@ -13755,13 +13761,13 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>241</v>
+        <v>401</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13769,10 +13775,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13792,23 +13798,19 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>153</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>244</v>
+        <v>154</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13856,7 +13858,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13868,7 +13870,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13877,10 +13879,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13891,23 +13893,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13919,20 +13919,18 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>420</v>
+        <v>181</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>420</v>
+        <v>182</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13956,31 +13954,31 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>379</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13992,7 +13990,7 @@
         <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
@@ -14004,10 +14002,10 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>387</v>
+        <v>157</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14015,10 +14013,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14029,7 +14027,7 @@
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -14038,19 +14036,23 @@
         <v>83</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -14098,19 +14100,19 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -14119,10 +14121,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -14133,21 +14135,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>83</v>
@@ -14159,17 +14161,15 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14206,31 +14206,31 @@
         <v>83</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14253,14 +14253,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14276,23 +14276,21 @@
         <v>83</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
       </c>
@@ -14328,19 +14326,19 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14352,7 +14350,7 @@
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>83</v>
@@ -14361,10 +14359,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14375,10 +14373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14386,7 +14384,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>94</v>
@@ -14398,25 +14396,29 @@
         <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>83</v>
@@ -14458,7 +14460,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14470,7 +14472,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14479,10 +14481,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14493,21 +14495,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14516,19 +14518,19 @@
         <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14566,31 +14568,31 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14599,10 +14601,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14613,10 +14615,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14639,26 +14641,24 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>83</v>
@@ -14700,7 +14700,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14721,10 +14721,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14735,10 +14735,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14764,15 +14764,15 @@
         <v>153</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14841,10 +14841,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14855,10 +14855,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>94</v>
@@ -14881,24 +14881,26 @@
         <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O104" t="s" s="2">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>83</v>
@@ -14940,7 +14942,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14961,10 +14963,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14975,10 +14977,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15004,14 +15006,16 @@
         <v>153</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O105" t="s" s="2">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15060,7 +15064,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15081,10 +15085,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -15098,15 +15102,17 @@
         <v>432</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>94</v>
@@ -15118,22 +15124,22 @@
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>235</v>
+        <v>434</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>237</v>
+        <v>435</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15158,13 +15164,13 @@
         <v>83</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>83</v>
@@ -15182,13 +15188,13 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>239</v>
+        <v>393</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>83</v>
@@ -15203,13 +15209,13 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>241</v>
+        <v>401</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15217,10 +15223,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15240,23 +15246,19 @@
         <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>153</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>244</v>
+        <v>154</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>83</v>
       </c>
@@ -15304,7 +15306,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15316,7 +15318,7 @@
         <v>83</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>83</v>
@@ -15325,10 +15327,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15339,23 +15341,21 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>83</v>
@@ -15367,20 +15367,18 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>436</v>
+        <v>181</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>436</v>
+        <v>182</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>83</v>
       </c>
@@ -15404,29 +15402,31 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>379</v>
+        <v>161</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15438,7 +15438,7 @@
         <v>83</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>83</v>
@@ -15450,10 +15450,10 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>387</v>
+        <v>157</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
@@ -15464,7 +15464,7 @@
         <v>438</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15475,7 +15475,7 @@
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>83</v>
@@ -15484,19 +15484,23 @@
         <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15544,19 +15548,19 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>83</v>
@@ -15565,10 +15569,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15582,18 +15586,18 @@
         <v>439</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>83</v>
@@ -15605,17 +15609,15 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15652,31 +15654,31 @@
         <v>83</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>83</v>
@@ -15702,11 +15704,11 @@
         <v>440</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15722,23 +15724,21 @@
         <v>83</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15774,19 +15774,19 @@
         <v>83</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15798,7 +15798,7 @@
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -15807,10 +15807,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15824,7 +15824,7 @@
         <v>441</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>94</v>
@@ -15844,25 +15844,29 @@
         <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>83</v>
@@ -15904,7 +15908,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15916,7 +15920,7 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
@@ -15925,10 +15929,10 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15939,21 +15943,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -15962,19 +15966,19 @@
         <v>83</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16012,31 +16016,31 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
@@ -16045,10 +16049,10 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -16059,10 +16063,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16085,26 +16089,24 @@
         <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16146,7 +16148,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16167,10 +16169,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -16181,10 +16183,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16210,15 +16212,15 @@
         <v>153</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -16266,7 +16268,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16287,10 +16289,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16301,10 +16303,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16312,7 +16314,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>94</v>
@@ -16327,24 +16329,26 @@
         <v>95</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O116" t="s" s="2">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>447</v>
+        <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>83</v>
@@ -16386,7 +16390,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16407,10 +16411,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16424,7 +16428,7 @@
         <v>448</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16450,14 +16454,16 @@
         <v>153</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O117" t="s" s="2">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16506,7 +16512,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16527,10 +16533,10 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16544,15 +16550,17 @@
         <v>449</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>94</v>
@@ -16564,22 +16572,22 @@
         <v>83</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>235</v>
+        <v>451</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>236</v>
+        <v>451</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>237</v>
+        <v>435</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>238</v>
+        <v>397</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16604,13 +16612,11 @@
         <v>83</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>83</v>
+        <v>452</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>83</v>
@@ -16628,13 +16634,13 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>239</v>
+        <v>393</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>83</v>
@@ -16649,13 +16655,13 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>241</v>
+        <v>401</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>83</v>
@@ -16663,10 +16669,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16686,23 +16692,19 @@
         <v>83</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>153</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>244</v>
+        <v>154</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16750,7 +16752,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16762,7 +16764,7 @@
         <v>83</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>83</v>
@@ -16771,10 +16773,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16785,21 +16787,21 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>452</v>
+        <v>180</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>83</v>
@@ -16808,23 +16810,21 @@
         <v>83</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>453</v>
+        <v>181</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>453</v>
+        <v>182</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -16848,69 +16848,69 @@
         <v>83</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>451</v>
+        <v>161</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>462</v>
+        <v>157</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>465</v>
+        <v>413</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16921,7 +16921,7 @@
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
@@ -16930,19 +16930,23 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -16990,19 +16994,19 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>83</v>
@@ -17011,10 +17015,10 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17025,21 +17029,21 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>83</v>
@@ -17051,17 +17055,15 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17098,31 +17100,31 @@
         <v>83</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>83</v>
@@ -17145,14 +17147,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>467</v>
+        <v>417</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17168,23 +17170,21 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>468</v>
+        <v>181</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>468</v>
+        <v>182</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>83</v>
       </c>
@@ -17220,19 +17220,19 @@
         <v>83</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17244,7 +17244,7 @@
         <v>83</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>83</v>
@@ -17253,10 +17253,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17267,10 +17267,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>469</v>
+        <v>419</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>94</v>
@@ -17290,25 +17290,29 @@
         <v>83</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q124" s="2"/>
       <c r="R124" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="S124" t="s" s="2">
         <v>83</v>
@@ -17350,7 +17354,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17362,7 +17366,7 @@
         <v>83</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>83</v>
@@ -17371,10 +17375,10 @@
         <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>157</v>
+        <v>207</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>83</v>
@@ -17385,21 +17389,21 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>470</v>
+        <v>422</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>83</v>
@@ -17408,19 +17412,19 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17458,31 +17462,31 @@
         <v>83</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>83</v>
@@ -17491,10 +17495,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
@@ -17505,10 +17509,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17516,7 +17520,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>94</v>
@@ -17531,26 +17535,24 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>427</v>
+        <v>462</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>83</v>
@@ -17592,7 +17594,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17613,10 +17615,10 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>83</v>
@@ -17627,10 +17629,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17656,15 +17658,15 @@
         <v>153</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>83</v>
       </c>
@@ -17712,7 +17714,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -17733,10 +17735,10 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>83</v>
@@ -17747,10 +17749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17758,7 +17760,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>94</v>
@@ -17773,24 +17775,26 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O128" t="s" s="2">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>474</v>
+        <v>83</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>83</v>
@@ -17832,7 +17836,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17853,10 +17857,10 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
@@ -17867,10 +17871,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17896,14 +17900,16 @@
         <v>153</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17913,7 +17919,7 @@
         <v>83</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>83</v>
@@ -17952,7 +17958,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17973,10 +17979,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17987,18 +17993,18 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>94</v>
@@ -18013,19 +18019,19 @@
         <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>235</v>
+        <v>468</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>237</v>
+        <v>469</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>238</v>
+        <v>470</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -18050,13 +18056,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>83</v>
+        <v>473</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -18074,10 +18080,10 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>239</v>
+        <v>466</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>94</v>
@@ -18089,30 +18095,30 @@
         <v>106</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>240</v>
+        <v>476</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>241</v>
+        <v>477</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18132,23 +18138,19 @@
         <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>153</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>244</v>
+        <v>154</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>83</v>
       </c>
@@ -18196,7 +18198,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18208,7 +18210,7 @@
         <v>83</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>83</v>
@@ -18217,10 +18219,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
@@ -18231,21 +18233,21 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>83</v>
@@ -18254,23 +18256,21 @@
         <v>83</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>481</v>
+        <v>181</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>481</v>
+        <v>182</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>83</v>
       </c>
@@ -18306,46 +18306,46 @@
         <v>83</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>479</v>
+        <v>161</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>485</v>
+        <v>83</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>486</v>
+        <v>157</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AP132" t="s" s="2">
         <v>83</v>
@@ -18353,10 +18353,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18379,18 +18379,20 @@
         <v>95</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>489</v>
+        <v>186</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>83</v>
       </c>
@@ -18438,7 +18440,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>488</v>
+        <v>191</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18459,13 +18461,13 @@
         <v>83</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>461</v>
+        <v>192</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>492</v>
+        <v>193</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AP133" t="s" s="2">
         <v>83</v>
@@ -18473,14 +18475,14 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>494</v>
+        <v>83</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -18496,23 +18498,19 @@
         <v>83</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>495</v>
+        <v>153</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>496</v>
+        <v>154</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>83</v>
       </c>
@@ -18560,7 +18558,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>493</v>
+        <v>156</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -18572,22 +18570,22 @@
         <v>83</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>499</v>
+        <v>83</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>501</v>
+        <v>157</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AP134" t="s" s="2">
         <v>83</v>
@@ -18595,21 +18593,21 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>504</v>
+        <v>180</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>83</v>
@@ -18618,23 +18616,21 @@
         <v>83</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>505</v>
+        <v>139</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>506</v>
+        <v>181</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>506</v>
+        <v>182</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>83</v>
       </c>
@@ -18670,46 +18666,46 @@
         <v>83</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>503</v>
+        <v>161</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>511</v>
+        <v>157</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>512</v>
+        <v>83</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>83</v>
@@ -18717,10 +18713,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18743,24 +18739,26 @@
         <v>95</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>514</v>
+        <v>108</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>515</v>
+        <v>200</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>515</v>
+        <v>201</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O136" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q136" s="2"/>
       <c r="R136" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="S136" t="s" s="2">
         <v>83</v>
@@ -18802,7 +18800,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>513</v>
+        <v>205</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -18823,13 +18821,13 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>517</v>
+        <v>206</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>518</v>
+        <v>207</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>519</v>
+        <v>83</v>
       </c>
       <c r="AP136" t="s" s="2">
         <v>83</v>
@@ -18837,10 +18835,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18851,7 +18849,7 @@
         <v>81</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>83</v>
@@ -18863,20 +18861,18 @@
         <v>95</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>521</v>
+        <v>153</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>522</v>
+        <v>210</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>522</v>
+        <v>211</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>83</v>
       </c>
@@ -18924,13 +18920,13 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>520</v>
+        <v>213</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>83</v>
@@ -18939,19 +18935,19 @@
         <v>106</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>526</v>
+        <v>214</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>527</v>
+        <v>215</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
       <c r="AP137" t="s" s="2">
         <v>83</v>
@@ -18959,10 +18955,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18970,7 +18966,7 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>94</v>
@@ -18985,26 +18981,24 @@
         <v>95</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>530</v>
+        <v>218</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>532</v>
+        <v>220</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="S138" t="s" s="2">
         <v>83</v>
@@ -19046,7 +19040,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>529</v>
+        <v>221</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19055,7 +19049,7 @@
         <v>94</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>106</v>
@@ -19064,27 +19058,27 @@
         <v>83</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>535</v>
+        <v>222</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>536</v>
+        <v>83</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>537</v>
+        <v>490</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>537</v>
+        <v>490</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19104,22 +19098,20 @@
         <v>83</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>538</v>
+        <v>226</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>540</v>
+        <v>228</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>83</v>
@@ -19129,7 +19121,7 @@
         <v>83</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>83</v>
@@ -19144,13 +19136,13 @@
         <v>83</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>541</v>
+        <v>83</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>542</v>
+        <v>83</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>83</v>
@@ -19168,7 +19160,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>537</v>
+        <v>229</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19177,7 +19169,7 @@
         <v>94</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>106</v>
@@ -19189,10 +19181,10 @@
         <v>83</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>545</v>
+        <v>231</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
@@ -19203,21 +19195,21 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>546</v>
+        <v>492</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>546</v>
+        <v>492</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>83</v>
@@ -19226,22 +19218,22 @@
         <v>83</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>548</v>
+        <v>235</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>548</v>
+        <v>236</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>549</v>
+        <v>237</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>550</v>
+        <v>238</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19266,13 +19258,13 @@
         <v>83</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>541</v>
+        <v>83</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>552</v>
+        <v>83</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
@@ -19290,13 +19282,13 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>546</v>
+        <v>239</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>83</v>
@@ -19308,27 +19300,27 @@
         <v>83</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>554</v>
+        <v>240</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>555</v>
+        <v>241</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>556</v>
+        <v>83</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>557</v>
+        <v>493</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19339,7 +19331,7 @@
         <v>81</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>83</v>
@@ -19348,22 +19340,22 @@
         <v>83</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>558</v>
+        <v>153</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>559</v>
+        <v>244</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>559</v>
+        <v>245</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>560</v>
+        <v>246</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>561</v>
+        <v>247</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>83</v>
@@ -19412,13 +19404,13 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>557</v>
+        <v>248</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>83</v>
@@ -19433,10 +19425,10 @@
         <v>83</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>562</v>
+        <v>249</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>563</v>
+        <v>250</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
@@ -19447,10 +19439,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>564</v>
+        <v>494</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>564</v>
+        <v>494</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19458,7 +19450,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>94</v>
@@ -19470,21 +19462,23 @@
         <v>83</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>171</v>
+        <v>495</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>565</v>
+        <v>496</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>565</v>
+        <v>496</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>83</v>
       </c>
@@ -19508,13 +19502,13 @@
         <v>83</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>567</v>
+        <v>83</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>83</v>
@@ -19532,7 +19526,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>564</v>
+        <v>494</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19547,30 +19541,30 @@
         <v>106</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>569</v>
+        <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>83</v>
+        <v>502</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>572</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>573</v>
+        <v>503</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>573</v>
+        <v>503</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19581,7 +19575,7 @@
         <v>81</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>83</v>
@@ -19590,23 +19584,21 @@
         <v>83</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>171</v>
+        <v>504</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>574</v>
+        <v>505</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>574</v>
+        <v>505</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>83</v>
       </c>
@@ -19630,13 +19622,13 @@
         <v>83</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>578</v>
+        <v>83</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>83</v>
@@ -19654,13 +19646,13 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>573</v>
+        <v>503</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>83</v>
@@ -19675,13 +19667,13 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>579</v>
+        <v>476</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>580</v>
+        <v>507</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>83</v>
+        <v>502</v>
       </c>
       <c r="AP143" t="s" s="2">
         <v>83</v>
@@ -19689,14 +19681,14 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19712,21 +19704,23 @@
         <v>83</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>582</v>
+        <v>510</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>583</v>
+        <v>511</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>583</v>
+        <v>511</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
       </c>
@@ -19774,7 +19768,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>581</v>
+        <v>508</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19789,34 +19783,34 @@
         <v>106</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>83</v>
+        <v>514</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>585</v>
+        <v>83</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>586</v>
+        <v>515</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>587</v>
+        <v>516</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>588</v>
+        <v>83</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>589</v>
+        <v>518</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>589</v>
+        <v>518</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19832,21 +19826,23 @@
         <v>83</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>591</v>
+        <v>521</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>591</v>
+        <v>521</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>83</v>
       </c>
@@ -19894,7 +19890,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>589</v>
+        <v>518</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -19909,30 +19905,30 @@
         <v>106</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>593</v>
+        <v>83</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>594</v>
+        <v>525</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>595</v>
+        <v>526</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>596</v>
+        <v>83</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>597</v>
+        <v>528</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>597</v>
+        <v>528</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19943,7 +19939,7 @@
         <v>81</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>83</v>
@@ -19952,23 +19948,21 @@
         <v>83</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>598</v>
+        <v>529</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>599</v>
+        <v>530</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>599</v>
+        <v>530</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>83</v>
       </c>
@@ -20016,19 +20010,19 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>597</v>
+        <v>528</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>602</v>
+        <v>106</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>83</v>
@@ -20037,13 +20031,13 @@
         <v>83</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>603</v>
+        <v>532</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>604</v>
+        <v>533</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="AP146" t="s" s="2">
         <v>83</v>
@@ -20051,10 +20045,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>605</v>
+        <v>535</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>605</v>
+        <v>535</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20065,7 +20059,7 @@
         <v>81</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>83</v>
@@ -20074,19 +20068,23 @@
         <v>83</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>153</v>
+        <v>536</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>154</v>
+        <v>537</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
       </c>
@@ -20134,34 +20132,34 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>156</v>
+        <v>535</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>83</v>
+        <v>540</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>83</v>
+        <v>541</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>157</v>
+        <v>542</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>83</v>
+        <v>543</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>83</v>
@@ -20169,21 +20167,21 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>83</v>
@@ -20192,21 +20190,23 @@
         <v>83</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>181</v>
+        <v>545</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>182</v>
+        <v>545</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>83</v>
       </c>
@@ -20254,80 +20254,80 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>161</v>
+        <v>544</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>83</v>
+        <v>548</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>83</v>
+        <v>550</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>157</v>
+        <v>302</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP148" t="s" s="2">
-        <v>83</v>
+        <v>551</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>607</v>
+        <v>552</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>607</v>
+        <v>552</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>608</v>
+        <v>83</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>609</v>
+        <v>553</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>610</v>
+        <v>553</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>183</v>
+        <v>554</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>340</v>
+        <v>555</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20352,13 +20352,13 @@
         <v>83</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>83</v>
+        <v>558</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
@@ -20376,19 +20376,19 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>611</v>
+        <v>552</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>83</v>
+        <v>559</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>83</v>
@@ -20397,10 +20397,10 @@
         <v>83</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>137</v>
+        <v>560</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>83</v>
@@ -20411,21 +20411,21 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>612</v>
+        <v>561</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>612</v>
+        <v>561</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>83</v>
+        <v>562</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>83</v>
@@ -20437,16 +20437,20 @@
         <v>83</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>613</v>
+        <v>171</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>614</v>
+        <v>563</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
       </c>
@@ -20470,13 +20474,13 @@
         <v>83</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>83</v>
+        <v>556</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>83</v>
+        <v>566</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
@@ -20494,16 +20498,16 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>612</v>
+        <v>561</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>616</v>
+        <v>83</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
@@ -20512,27 +20516,27 @@
         <v>83</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>617</v>
+        <v>569</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>83</v>
+        <v>571</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20543,7 +20547,7 @@
         <v>81</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>83</v>
@@ -20555,16 +20559,20 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>620</v>
+        <v>574</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
       </c>
@@ -20612,16 +20620,16 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>616</v>
+        <v>83</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>106</v>
@@ -20633,10 +20641,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>622</v>
+        <v>578</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20647,10 +20655,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>623</v>
+        <v>579</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>623</v>
+        <v>579</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20676,17 +20684,15 @@
         <v>171</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>624</v>
+        <v>580</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>625</v>
+        <v>580</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>83</v>
       </c>
@@ -20710,13 +20716,13 @@
         <v>83</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>118</v>
+        <v>471</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>629</v>
+        <v>583</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>83</v>
@@ -20734,7 +20740,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>623</v>
+        <v>579</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20752,27 +20758,27 @@
         <v>83</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>555</v>
+        <v>586</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>83</v>
+        <v>587</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>632</v>
+        <v>588</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>632</v>
+        <v>588</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20783,7 +20789,7 @@
         <v>81</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>83</v>
@@ -20798,16 +20804,16 @@
         <v>171</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>633</v>
+        <v>589</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>634</v>
+        <v>589</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>635</v>
+        <v>590</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>636</v>
+        <v>591</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>83</v>
@@ -20832,13 +20838,13 @@
         <v>83</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>637</v>
+        <v>592</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>638</v>
+        <v>593</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>83</v>
@@ -20856,13 +20862,13 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>632</v>
+        <v>588</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>83</v>
@@ -20874,13 +20880,13 @@
         <v>83</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>630</v>
+        <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>631</v>
+        <v>594</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -20891,10 +20897,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20917,18 +20923,18 @@
         <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>641</v>
+        <v>598</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>83</v>
       </c>
@@ -20976,7 +20982,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -20994,27 +21000,27 @@
         <v>83</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>83</v>
+        <v>600</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>83</v>
+        <v>601</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>644</v>
+        <v>602</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>83</v>
+        <v>603</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21037,15 +21043,17 @@
         <v>83</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>153</v>
+        <v>605</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N155" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21094,7 +21102,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21112,27 +21120,27 @@
         <v>83</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>83</v>
+        <v>608</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>648</v>
+        <v>610</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>83</v>
+        <v>611</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>649</v>
+        <v>612</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>649</v>
+        <v>612</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21152,21 +21160,23 @@
         <v>83</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>650</v>
+        <v>613</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>651</v>
+        <v>614</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>651</v>
+        <v>614</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O156" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
       </c>
@@ -21214,7 +21224,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>649</v>
+        <v>612</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21226,7 +21236,7 @@
         <v>83</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>106</v>
+        <v>617</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>83</v>
@@ -21235,10 +21245,10 @@
         <v>83</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>653</v>
+        <v>618</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>654</v>
+        <v>619</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
@@ -21249,10 +21259,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>655</v>
+        <v>620</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>655</v>
+        <v>620</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21263,7 +21273,7 @@
         <v>81</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>83</v>
@@ -21272,20 +21282,18 @@
         <v>83</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>656</v>
+        <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>657</v>
+        <v>154</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>658</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -21334,19 +21342,19 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>655</v>
+        <v>156</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>83</v>
@@ -21355,10 +21363,10 @@
         <v>83</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>653</v>
+        <v>83</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>659</v>
+        <v>157</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21369,14 +21377,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>660</v>
+        <v>621</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>660</v>
+        <v>621</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21392,23 +21400,21 @@
         <v>83</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>598</v>
+        <v>139</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>661</v>
+        <v>181</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>661</v>
+        <v>182</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>663</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>83</v>
       </c>
@@ -21456,7 +21462,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>660</v>
+        <v>161</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21468,7 +21474,7 @@
         <v>83</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>83</v>
@@ -21477,10 +21483,10 @@
         <v>83</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>664</v>
+        <v>83</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>665</v>
+        <v>157</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
@@ -21491,42 +21497,46 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>666</v>
+        <v>622</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>666</v>
+        <v>622</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>83</v>
+        <v>623</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>154</v>
+        <v>624</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
       </c>
@@ -21574,19 +21584,19 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>156</v>
+        <v>626</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>83</v>
@@ -21598,7 +21608,7 @@
         <v>83</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>83</v>
@@ -21609,21 +21619,21 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>667</v>
+        <v>627</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>667</v>
+        <v>627</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>83</v>
@@ -21635,17 +21645,15 @@
         <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>139</v>
+        <v>628</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>181</v>
+        <v>629</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -21694,19 +21702,19 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>161</v>
+        <v>627</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>83</v>
+        <v>631</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>83</v>
@@ -21715,10 +21723,10 @@
         <v>83</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>83</v>
+        <v>632</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>157</v>
+        <v>633</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>
@@ -21729,46 +21737,42 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>668</v>
+        <v>634</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>668</v>
+        <v>634</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>608</v>
+        <v>83</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>139</v>
+        <v>628</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>83</v>
       </c>
@@ -21816,19 +21820,19 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>83</v>
+        <v>631</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>83</v>
@@ -21837,10 +21841,10 @@
         <v>83</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>83</v>
+        <v>632</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>137</v>
+        <v>637</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>83</v>
@@ -21851,10 +21855,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21862,7 +21866,7 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G162" t="s" s="2">
         <v>94</v>
@@ -21874,22 +21878,22 @@
         <v>83</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>670</v>
+        <v>639</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>671</v>
+        <v>640</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>455</v>
+        <v>642</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -21914,13 +21918,13 @@
         <v>83</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>456</v>
+        <v>118</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>457</v>
+        <v>643</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>458</v>
+        <v>644</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
@@ -21938,10 +21942,10 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>94</v>
@@ -21956,16 +21960,16 @@
         <v>83</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>461</v>
+        <v>646</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>462</v>
+        <v>570</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>463</v>
+        <v>83</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>83</v>
@@ -21973,10 +21977,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21987,7 +21991,7 @@
         <v>81</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>83</v>
@@ -21996,22 +22000,22 @@
         <v>83</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>675</v>
+        <v>171</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>532</v>
+        <v>651</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22036,13 +22040,13 @@
         <v>83</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>83</v>
+        <v>652</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>83</v>
+        <v>653</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>83</v>
@@ -22060,13 +22064,13 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>83</v>
@@ -22078,27 +22082,27 @@
         <v>83</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>679</v>
+        <v>645</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>535</v>
+        <v>646</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>302</v>
+        <v>570</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>536</v>
+        <v>83</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22121,19 +22125,17 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>171</v>
+        <v>655</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>681</v>
+        <v>656</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>540</v>
+        <v>658</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -22158,13 +22160,13 @@
         <v>83</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>541</v>
+        <v>83</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>542</v>
+        <v>83</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>83</v>
@@ -22182,7 +22184,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -22191,7 +22193,7 @@
         <v>94</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>106</v>
@@ -22203,10 +22205,10 @@
         <v>83</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>545</v>
+        <v>659</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>83</v>
@@ -22217,21 +22219,21 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>83</v>
@@ -22243,20 +22245,16 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>688</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>83</v>
       </c>
@@ -22280,13 +22278,13 @@
         <v>83</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>541</v>
+        <v>83</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>551</v>
+        <v>83</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>552</v>
+        <v>83</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -22304,13 +22302,13 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>83</v>
@@ -22322,27 +22320,27 @@
         <v>83</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>554</v>
+        <v>632</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>555</v>
+        <v>663</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>556</v>
+        <v>83</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22362,23 +22360,21 @@
         <v>83</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>84</v>
+        <v>665</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>691</v>
+        <v>666</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>693</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>83</v>
       </c>
@@ -22426,7 +22422,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>689</v>
+        <v>664</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22447,15 +22443,1227 @@
         <v>83</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>603</v>
+        <v>668</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>604</v>
+        <v>669</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP166" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="P168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP168" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O170" s="2"/>
+      <c r="P170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O175" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="P175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP175" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="P176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AO176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP176" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -1058,7 +1058,7 @@
     <t>root</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalRootBodyStructure_VS</t>
   </si>
   <si>
     <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:root.id</t>
@@ -1106,37 +1106,37 @@
     <t>Observation.extension.extension.value[x].coding.userSelected</t>
   </si>
   <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface</t>
-  </si>
-  <si>
-    <t>suface</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_VS</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.id</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.system</t>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface</t>
+  </si>
+  <si>
+    <t>surface</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.system</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_CS</t>
   </si>
   <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.version</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.code</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.display</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:suface.userSelected</t>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.version</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.code</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.display</t>
+  </si>
+  <si>
+    <t>Observation.extension:bodyStructure.extension:qualifier.value[x].coding:surface.userSelected</t>
   </si>
   <si>
     <t>Observation.extension:bodyStructure.extension:qualifier.value[x].text</t>
@@ -11750,7 +11750,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -12714,7 +12714,7 @@
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>83</v>
@@ -13800,7 +13800,7 @@
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -14510,7 +14510,7 @@
         <v>81</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7481" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7035" uniqueCount="729">
   <si>
     <t>Property</t>
   </si>
@@ -1143,55 +1143,6 @@
   </si>
   <si>
     <t>Observation.extension.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root</t>
-  </si>
-  <si>
-    <t>qualifier/root</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.id</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.url</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/root.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface</t>
-  </si>
-  <si>
-    <t>qualifier/surface</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.id</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.extension</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.url</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.extension:bodyStructure.extension:qualifier.extension:qualifier/surface.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Observation.extension:bodyStructure.url</t>
@@ -2628,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP196"/>
+  <dimension ref="A1:AP184"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="108.2890625" customWidth="true" bestFit="true"/>
@@ -11799,7 +11750,7 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
@@ -12763,7 +12714,7 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
@@ -13787,20 +13738,18 @@
         <v>368</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13812,22 +13761,24 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>83</v>
@@ -13869,19 +13820,19 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>83</v>
@@ -13893,7 +13844,7 @@
         <v>83</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13907,7 +13858,7 @@
         <v>370</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13918,7 +13869,7 @@
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13930,13 +13881,13 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>153</v>
+        <v>314</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13987,7 +13938,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13999,7 +13950,7 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -14011,7 +13962,7 @@
         <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -14025,24 +13976,24 @@
         <v>371</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>286</v>
+        <v>371</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>83</v>
@@ -14051,13 +14002,17 @@
         <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>140</v>
+        <v>372</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -14093,19 +14048,19 @@
         <v>83</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>375</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14129,7 +14084,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -14140,10 +14095,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14151,10 +14106,10 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -14163,21 +14118,23 @@
         <v>83</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>108</v>
+        <v>377</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>164</v>
+        <v>378</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>165</v>
+        <v>378</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -14225,34 +14182,34 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -14260,21 +14217,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>290</v>
+        <v>385</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>83</v>
@@ -14283,19 +14240,23 @@
         <v>83</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>172</v>
+        <v>388</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -14331,23 +14292,25 @@
         <v>83</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AC98" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>175</v>
+        <v>385</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>83</v>
@@ -14356,16 +14319,16 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>137</v>
+        <v>393</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14376,23 +14339,21 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>83</v>
@@ -14401,18 +14362,20 @@
         <v>83</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>396</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14437,11 +14400,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z99" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14459,13 +14424,13 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>175</v>
+        <v>394</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>83</v>
@@ -14474,16 +14439,16 @@
         <v>106</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>137</v>
+        <v>401</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14494,44 +14459,46 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>140</v>
+        <v>403</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14555,13 +14522,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14579,34 +14546,34 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>161</v>
+        <v>402</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14614,10 +14581,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>284</v>
+        <v>413</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14625,10 +14592,10 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14640,16 +14607,20 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>154</v>
+        <v>415</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
       </c>
@@ -14673,43 +14644,41 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="AC101" s="2"/>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>156</v>
+        <v>413</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14721,10 +14690,10 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>157</v>
+        <v>421</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -14732,21 +14701,23 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="D102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>83</v>
@@ -14758,16 +14729,20 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>140</v>
+        <v>425</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -14791,31 +14766,29 @@
         <v>83</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>161</v>
+        <v>413</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14827,7 +14800,7 @@
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>83</v>
@@ -14839,10 +14812,10 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -14850,10 +14823,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>381</v>
+        <v>428</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>288</v>
+        <v>429</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14861,7 +14834,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>94</v>
@@ -14876,17 +14849,15 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14935,10 +14906,10 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>94</v>
@@ -14959,7 +14930,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14970,21 +14941,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>290</v>
+        <v>431</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>83</v>
@@ -14996,15 +14967,17 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>314</v>
+        <v>139</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15041,9 +15014,11 @@
         <v>83</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>83</v>
       </c>
@@ -15051,19 +15026,19 @@
         <v>143</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>83</v>
@@ -15075,7 +15050,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15086,14 +15061,12 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>83</v>
       </c>
@@ -15102,7 +15075,7 @@
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -15111,19 +15084,23 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
       </c>
@@ -15147,11 +15124,13 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y105" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z105" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -15169,13 +15148,13 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>83</v>
@@ -15190,10 +15169,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -15204,10 +15183,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>163</v>
+        <v>435</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15215,7 +15194,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>94</v>
@@ -15230,24 +15209,22 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>83</v>
@@ -15289,10 +15266,10 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>94</v>
@@ -15313,7 +15290,7 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15324,21 +15301,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>170</v>
+        <v>437</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>83</v>
@@ -15350,15 +15327,17 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>314</v>
+        <v>139</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15395,31 +15374,31 @@
         <v>83</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>83</v>
@@ -15431,7 +15410,7 @@
         <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15442,52 +15421,52 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>387</v>
+        <v>438</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J108" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="J108" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K108" t="s" s="2">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>388</v>
+        <v>200</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>389</v>
+        <v>201</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>390</v>
+        <v>203</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>83</v>
+        <v>440</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>83</v>
@@ -15529,19 +15508,19 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>391</v>
+        <v>205</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>83</v>
@@ -15550,10 +15529,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15564,10 +15543,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>392</v>
+        <v>441</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15578,7 +15557,7 @@
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>83</v>
@@ -15590,20 +15569,18 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>394</v>
+        <v>210</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>394</v>
+        <v>211</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15651,13 +15628,13 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>392</v>
+        <v>213</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>83</v>
@@ -15666,19 +15643,19 @@
         <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>398</v>
+        <v>214</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>399</v>
+        <v>215</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
@@ -15686,21 +15663,21 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>83</v>
@@ -15712,26 +15689,24 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>403</v>
+        <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>404</v>
+        <v>218</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>406</v>
+        <v>220</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>83</v>
@@ -15773,13 +15748,13 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>401</v>
+        <v>221</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
@@ -15788,16 +15763,16 @@
         <v>106</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>408</v>
+        <v>222</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>409</v>
+        <v>223</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15808,21 +15783,21 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -15834,18 +15809,18 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>412</v>
+        <v>153</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>413</v>
+        <v>226</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15893,13 +15868,13 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>410</v>
+        <v>229</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
@@ -15908,16 +15883,16 @@
         <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>416</v>
+        <v>230</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>417</v>
+        <v>231</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15928,10 +15903,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15939,7 +15914,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>94</v>
@@ -15948,25 +15923,25 @@
         <v>83</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>419</v>
+        <v>235</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>419</v>
+        <v>236</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>420</v>
+        <v>237</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>421</v>
+        <v>238</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15991,13 +15966,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16015,10 +15990,10 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>418</v>
+        <v>239</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>94</v>
@@ -16030,19 +16005,19 @@
         <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>426</v>
+        <v>240</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>427</v>
+        <v>241</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16050,10 +16025,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16061,10 +16036,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -16073,22 +16048,22 @@
         <v>83</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>431</v>
+        <v>244</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>431</v>
+        <v>245</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>432</v>
+        <v>246</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>433</v>
+        <v>247</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16113,35 +16088,37 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>435</v>
+        <v>83</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AC113" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>429</v>
+        <v>248</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>83</v>
@@ -16156,13 +16133,13 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>437</v>
+        <v>250</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -16170,13 +16147,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16186,7 +16163,7 @@
         <v>94</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>83</v>
@@ -16201,16 +16178,16 @@
         <v>171</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16235,11 +16212,13 @@
         <v>83</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y114" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="Z114" t="s" s="2">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16257,7 +16236,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16281,10 +16260,10 @@
         <v>83</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16292,10 +16271,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16410,10 +16389,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16530,10 +16509,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16652,10 +16631,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16770,10 +16749,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16890,10 +16869,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16935,7 +16914,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>83</v>
@@ -17012,10 +16991,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17132,10 +17111,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17175,7 +17154,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -17252,10 +17231,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17372,10 +17351,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17494,10 +17473,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17616,13 +17595,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>83</v>
@@ -17647,16 +17626,16 @@
         <v>171</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -17681,13 +17660,11 @@
         <v>83</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -17705,7 +17682,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17729,10 +17706,10 @@
         <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -17740,10 +17717,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17858,10 +17835,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17978,10 +17955,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18100,10 +18077,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18218,10 +18195,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18338,10 +18315,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18383,7 +18360,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>83</v>
@@ -18460,10 +18437,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18580,10 +18557,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18623,7 +18600,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>83</v>
@@ -18700,10 +18677,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18820,10 +18797,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18942,10 +18919,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19064,16 +19041,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C138" t="s" s="2">
         <v>486</v>
       </c>
+      <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19089,22 +19064,22 @@
         <v>83</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
@@ -19129,11 +19104,13 @@
         <v>83</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="Y138" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="Z138" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>83</v>
@@ -19151,13 +19128,13 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>83</v>
@@ -19166,30 +19143,30 @@
         <v>106</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>83</v>
+        <v>495</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>83</v>
+        <v>496</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>437</v>
+        <v>497</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19304,10 +19281,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>447</v>
+        <v>501</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19424,10 +19401,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19453,10 +19430,10 @@
         <v>186</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>187</v>
+        <v>503</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>188</v>
+        <v>503</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>189</v>
@@ -19546,10 +19523,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19664,10 +19641,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19784,10 +19761,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>455</v>
+        <v>506</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19795,7 +19772,7 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>94</v>
@@ -19829,7 +19806,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>83</v>
@@ -19906,10 +19883,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>458</v>
+        <v>507</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20026,10 +20003,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>460</v>
+        <v>508</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20069,7 +20046,7 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>83</v>
@@ -20146,10 +20123,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20192,7 +20169,7 @@
         <v>83</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>83</v>
+        <v>511</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>83</v>
@@ -20266,10 +20243,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20388,10 +20365,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20510,14 +20487,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20536,19 +20513,19 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>171</v>
+        <v>515</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20573,13 +20550,13 @@
         <v>83</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
@@ -20597,10 +20574,10 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>94</v>
@@ -20612,30 +20589,30 @@
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>511</v>
+        <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>515</v>
+        <v>83</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20646,7 +20623,7 @@
         <v>81</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>83</v>
@@ -20655,18 +20632,20 @@
         <v>83</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>153</v>
+        <v>524</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>154</v>
+        <v>525</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -20715,19 +20694,19 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>156</v>
+        <v>523</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>83</v>
@@ -20736,13 +20715,13 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>83</v>
+        <v>496</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>157</v>
+        <v>527</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>83</v>
+        <v>522</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
@@ -20750,21 +20729,21 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>180</v>
+        <v>529</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>83</v>
@@ -20773,21 +20752,23 @@
         <v>83</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>139</v>
+        <v>530</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>181</v>
+        <v>531</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>182</v>
+        <v>531</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O152" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
       </c>
@@ -20823,46 +20804,46 @@
         <v>83</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>161</v>
+        <v>528</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>83</v>
+        <v>535</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>157</v>
+        <v>536</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>83</v>
@@ -20870,21 +20851,21 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>83</v>
+        <v>539</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>83</v>
@@ -20896,19 +20877,19 @@
         <v>95</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>186</v>
+        <v>540</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>189</v>
+        <v>542</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>190</v>
+        <v>543</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>83</v>
@@ -20957,13 +20938,13 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>191</v>
+        <v>538</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>83</v>
@@ -20972,19 +20953,19 @@
         <v>106</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>83</v>
+        <v>544</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>192</v>
+        <v>545</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>193</v>
+        <v>546</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="AP153" t="s" s="2">
         <v>83</v>
@@ -20992,10 +20973,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21015,18 +20996,20 @@
         <v>83</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>153</v>
+        <v>549</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>154</v>
+        <v>550</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N154" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>83</v>
@@ -21075,7 +21058,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>156</v>
+        <v>548</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21087,7 +21070,7 @@
         <v>83</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>83</v>
@@ -21096,13 +21079,13 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>157</v>
+        <v>553</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="AP154" t="s" s="2">
         <v>83</v>
@@ -21110,14 +21093,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21133,21 +21116,23 @@
         <v>83</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>139</v>
+        <v>556</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>181</v>
+        <v>557</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>182</v>
+        <v>557</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
       </c>
@@ -21183,19 +21168,19 @@
         <v>83</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>161</v>
+        <v>555</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21207,22 +21192,22 @@
         <v>83</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>83</v>
+        <v>560</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>83</v>
+        <v>561</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>157</v>
+        <v>562</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>83</v>
+        <v>563</v>
       </c>
       <c r="AP155" t="s" s="2">
         <v>83</v>
@@ -21230,10 +21215,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>522</v>
+        <v>564</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21256,26 +21241,26 @@
         <v>95</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>200</v>
+        <v>565</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>201</v>
+        <v>565</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>202</v>
+        <v>566</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>203</v>
+        <v>567</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="S156" t="s" s="2">
         <v>83</v>
@@ -21317,7 +21302,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>205</v>
+        <v>564</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21326,7 +21311,7 @@
         <v>94</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>83</v>
+        <v>568</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>106</v>
@@ -21335,27 +21320,27 @@
         <v>83</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>206</v>
+        <v>570</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>207</v>
+        <v>302</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>83</v>
+        <v>571</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>523</v>
+        <v>572</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>523</v>
+        <v>572</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21375,21 +21360,23 @@
         <v>83</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>210</v>
+        <v>573</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>211</v>
+        <v>573</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O157" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
       </c>
@@ -21413,13 +21400,13 @@
         <v>83</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>83</v>
@@ -21437,7 +21424,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>213</v>
+        <v>572</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21446,7 +21433,7 @@
         <v>94</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>106</v>
@@ -21458,10 +21445,10 @@
         <v>83</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>215</v>
+        <v>580</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21472,21 +21459,21 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>524</v>
+        <v>581</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>83</v>
+        <v>582</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>83</v>
@@ -21495,27 +21482,29 @@
         <v>83</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>218</v>
+        <v>583</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="O158" t="s" s="2">
-        <v>220</v>
+        <v>585</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>83</v>
@@ -21533,13 +21522,13 @@
         <v>83</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>83</v>
+        <v>586</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>83</v>
+        <v>587</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>83</v>
@@ -21557,13 +21546,13 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>221</v>
+        <v>581</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>83</v>
@@ -21575,27 +21564,27 @@
         <v>83</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>83</v>
+        <v>588</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>222</v>
+        <v>589</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>223</v>
+        <v>590</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>83</v>
+        <v>591</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>526</v>
+        <v>592</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>526</v>
+        <v>592</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21606,7 +21595,7 @@
         <v>81</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>83</v>
@@ -21615,20 +21604,22 @@
         <v>83</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>153</v>
+        <v>593</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>226</v>
+        <v>594</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N159" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O159" t="s" s="2">
-        <v>228</v>
+        <v>596</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
@@ -21638,7 +21629,7 @@
         <v>83</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>527</v>
+        <v>83</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>83</v>
@@ -21677,13 +21668,13 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>229</v>
+        <v>592</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>83</v>
@@ -21698,10 +21689,10 @@
         <v>83</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>230</v>
+        <v>597</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>231</v>
+        <v>598</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>83</v>
@@ -21712,10 +21703,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>528</v>
+        <v>599</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>528</v>
+        <v>599</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21735,23 +21726,21 @@
         <v>83</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>235</v>
+        <v>600</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>236</v>
+        <v>600</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>83</v>
       </c>
@@ -21775,13 +21764,13 @@
         <v>83</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>83</v>
+        <v>602</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>83</v>
+        <v>603</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>83</v>
@@ -21799,7 +21788,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>239</v>
+        <v>599</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21817,27 +21806,27 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>83</v>
+        <v>604</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>240</v>
+        <v>605</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>241</v>
+        <v>606</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>83</v>
+        <v>607</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21857,22 +21846,22 @@
         <v>83</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>244</v>
+        <v>609</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>245</v>
+        <v>609</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>246</v>
+        <v>610</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>247</v>
+        <v>611</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -21897,13 +21886,13 @@
         <v>83</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>83</v>
+        <v>612</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>83</v>
+        <v>613</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>83</v>
@@ -21921,7 +21910,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>248</v>
+        <v>608</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -21942,10 +21931,10 @@
         <v>83</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>249</v>
+        <v>614</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>250</v>
+        <v>615</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>83</v>
@@ -21956,10 +21945,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>530</v>
+        <v>616</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>530</v>
+        <v>616</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21967,7 +21956,7 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G162" t="s" s="2">
         <v>94</v>
@@ -21979,23 +21968,21 @@
         <v>83</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>531</v>
+        <v>617</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>532</v>
+        <v>618</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>532</v>
+        <v>618</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>83</v>
       </c>
@@ -22043,7 +22030,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>530</v>
+        <v>616</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22058,30 +22045,30 @@
         <v>106</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>83</v>
+        <v>620</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>536</v>
+        <v>621</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>537</v>
+        <v>622</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>83</v>
+        <v>623</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>539</v>
+        <v>624</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>539</v>
+        <v>624</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22092,7 +22079,7 @@
         <v>81</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>83</v>
@@ -22101,19 +22088,19 @@
         <v>83</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>540</v>
+        <v>625</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>541</v>
+        <v>626</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>541</v>
+        <v>626</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>542</v>
+        <v>627</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22163,13 +22150,13 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>539</v>
+        <v>624</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>83</v>
@@ -22181,38 +22168,38 @@
         <v>83</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>83</v>
+        <v>628</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>512</v>
+        <v>629</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>543</v>
+        <v>630</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>83</v>
+        <v>631</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>83</v>
@@ -22221,22 +22208,22 @@
         <v>83</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>546</v>
+        <v>633</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>547</v>
+        <v>634</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>547</v>
+        <v>634</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>548</v>
+        <v>635</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>549</v>
+        <v>636</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -22285,34 +22272,34 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>106</v>
+        <v>637</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>550</v>
+        <v>83</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>551</v>
+        <v>638</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>552</v>
+        <v>639</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>83</v>
@@ -22320,14 +22307,14 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>554</v>
+        <v>640</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>554</v>
+        <v>640</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -22343,23 +22330,19 @@
         <v>83</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>556</v>
+        <v>153</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>557</v>
+        <v>154</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>83</v>
       </c>
@@ -22407,7 +22390,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>554</v>
+        <v>156</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22419,22 +22402,22 @@
         <v>83</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>560</v>
+        <v>83</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>561</v>
+        <v>83</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>562</v>
+        <v>157</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>563</v>
+        <v>83</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>83</v>
@@ -22442,21 +22425,21 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>564</v>
+        <v>641</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>564</v>
+        <v>641</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>83</v>
@@ -22465,19 +22448,19 @@
         <v>83</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>565</v>
+        <v>139</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>566</v>
+        <v>181</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>566</v>
+        <v>182</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>567</v>
+        <v>183</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22527,19 +22510,19 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>564</v>
+        <v>161</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>83</v>
@@ -22548,13 +22531,13 @@
         <v>83</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>568</v>
+        <v>83</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>569</v>
+        <v>157</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>570</v>
+        <v>83</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>83</v>
@@ -22562,14 +22545,14 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>571</v>
+        <v>642</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>571</v>
+        <v>642</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>83</v>
+        <v>643</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22582,25 +22565,25 @@
         <v>83</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J167" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>572</v>
+        <v>139</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>575</v>
+        <v>374</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>83</v>
@@ -22649,7 +22632,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>571</v>
+        <v>646</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22661,22 +22644,22 @@
         <v>83</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>576</v>
+        <v>83</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>578</v>
+        <v>137</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="AP167" t="s" s="2">
         <v>83</v>
@@ -22684,10 +22667,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22707,23 +22690,19 @@
         <v>83</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>171</v>
+        <v>648</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>581</v>
+        <v>649</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>83</v>
       </c>
@@ -22771,7 +22750,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22780,7 +22759,7 @@
         <v>94</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>584</v>
+        <v>651</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>106</v>
@@ -22789,27 +22768,27 @@
         <v>83</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>585</v>
+        <v>83</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>586</v>
+        <v>652</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>302</v>
+        <v>653</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>587</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22832,20 +22811,16 @@
         <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>171</v>
+        <v>648</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>83</v>
       </c>
@@ -22869,13 +22844,13 @@
         <v>83</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>592</v>
+        <v>83</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>593</v>
+        <v>83</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>594</v>
+        <v>83</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>83</v>
@@ -22893,7 +22868,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -22902,7 +22877,7 @@
         <v>94</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>595</v>
+        <v>651</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>106</v>
@@ -22914,10 +22889,10 @@
         <v>83</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>137</v>
+        <v>652</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>596</v>
+        <v>657</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -22928,21 +22903,21 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>598</v>
+        <v>83</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>83</v>
@@ -22957,16 +22932,16 @@
         <v>171</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>599</v>
+        <v>659</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>599</v>
+        <v>660</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>600</v>
+        <v>661</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>601</v>
+        <v>662</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>83</v>
@@ -22991,13 +22966,13 @@
         <v>83</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>592</v>
+        <v>118</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>602</v>
+        <v>663</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>603</v>
+        <v>664</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -23015,13 +22990,13 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>83</v>
@@ -23033,27 +23008,27 @@
         <v>83</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>604</v>
+        <v>665</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>605</v>
+        <v>666</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>607</v>
+        <v>83</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>608</v>
+        <v>667</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>608</v>
+        <v>667</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23076,19 +23051,19 @@
         <v>83</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>609</v>
+        <v>171</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>610</v>
+        <v>668</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>610</v>
+        <v>669</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>611</v>
+        <v>670</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>612</v>
+        <v>671</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -23113,13 +23088,13 @@
         <v>83</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>83</v>
+        <v>672</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>83</v>
+        <v>673</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>83</v>
@@ -23137,7 +23112,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>608</v>
+        <v>667</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23155,13 +23130,13 @@
         <v>83</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>83</v>
+        <v>665</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>613</v>
+        <v>666</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>83</v>
@@ -23172,10 +23147,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>615</v>
+        <v>674</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>615</v>
+        <v>674</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23198,18 +23173,18 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>171</v>
+        <v>675</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>616</v>
+        <v>676</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O172" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N172" s="2"/>
+      <c r="O172" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>83</v>
       </c>
@@ -23233,13 +23208,13 @@
         <v>83</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>618</v>
+        <v>83</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>619</v>
+        <v>83</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>83</v>
@@ -23257,7 +23232,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>615</v>
+        <v>674</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23275,27 +23250,27 @@
         <v>83</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>620</v>
+        <v>83</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>621</v>
+        <v>83</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>622</v>
+        <v>679</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>623</v>
+        <v>83</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23318,20 +23293,16 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>625</v>
+        <v>681</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>83</v>
       </c>
@@ -23355,13 +23326,13 @@
         <v>83</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>628</v>
+        <v>83</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>629</v>
+        <v>83</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>83</v>
@@ -23379,7 +23350,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -23400,10 +23371,10 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>631</v>
+        <v>683</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -23414,10 +23385,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23428,7 +23399,7 @@
         <v>81</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>83</v>
@@ -23437,19 +23408,19 @@
         <v>83</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>633</v>
+        <v>685</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>634</v>
+        <v>686</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>634</v>
+        <v>686</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>635</v>
+        <v>687</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23499,13 +23470,13 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>83</v>
@@ -23517,27 +23488,27 @@
         <v>83</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>636</v>
+        <v>83</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>637</v>
+        <v>688</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>638</v>
+        <v>689</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>639</v>
+        <v>83</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23548,7 +23519,7 @@
         <v>81</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>83</v>
@@ -23557,19 +23528,19 @@
         <v>83</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>641</v>
+        <v>691</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>642</v>
+        <v>692</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>642</v>
+        <v>692</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>643</v>
+        <v>693</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23619,13 +23590,13 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>640</v>
+        <v>690</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>83</v>
@@ -23637,27 +23608,27 @@
         <v>83</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>644</v>
+        <v>83</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>647</v>
+        <v>83</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23677,22 +23648,22 @@
         <v>83</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>83</v>
@@ -23741,7 +23712,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -23753,7 +23724,7 @@
         <v>83</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>653</v>
+        <v>106</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>83</v>
@@ -23762,10 +23733,10 @@
         <v>83</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>654</v>
+        <v>699</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>83</v>
@@ -23776,10 +23747,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23894,10 +23865,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>657</v>
+        <v>702</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>657</v>
+        <v>702</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24014,14 +23985,14 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -24043,16 +24014,16 @@
         <v>139</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>83</v>
@@ -24101,7 +24072,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24136,10 +24107,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24147,7 +24118,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>94</v>
@@ -24159,19 +24130,23 @@
         <v>83</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>664</v>
+        <v>171</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>665</v>
+        <v>705</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+        <v>706</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>83</v>
       </c>
@@ -24195,13 +24170,13 @@
         <v>83</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>83</v>
@@ -24219,16 +24194,16 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>667</v>
+        <v>83</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>106</v>
@@ -24237,16 +24212,16 @@
         <v>83</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>83</v>
+        <v>708</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>668</v>
+        <v>496</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>669</v>
+        <v>497</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>83</v>
@@ -24254,10 +24229,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>670</v>
+        <v>709</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>670</v>
+        <v>709</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24277,19 +24252,23 @@
         <v>83</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>664</v>
+        <v>710</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>671</v>
+        <v>711</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N181" s="2"/>
-      <c r="O181" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>83</v>
       </c>
@@ -24337,7 +24316,7 @@
         <v>83</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>670</v>
+        <v>709</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24346,7 +24325,7 @@
         <v>94</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>667</v>
+        <v>83</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>106</v>
@@ -24355,27 +24334,27 @@
         <v>83</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>83</v>
+        <v>714</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>668</v>
+        <v>570</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>673</v>
+        <v>302</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP181" t="s" s="2">
-        <v>83</v>
+        <v>571</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24401,16 +24380,16 @@
         <v>171</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>676</v>
+        <v>717</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>677</v>
+        <v>718</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>678</v>
+        <v>575</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>83</v>
@@ -24435,13 +24414,13 @@
         <v>83</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>679</v>
+        <v>577</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>680</v>
+        <v>578</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>83</v>
@@ -24459,7 +24438,7 @@
         <v>83</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>674</v>
+        <v>715</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24468,7 +24447,7 @@
         <v>94</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>106</v>
@@ -24477,13 +24456,13 @@
         <v>83</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>681</v>
+        <v>83</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>682</v>
+        <v>137</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>83</v>
@@ -24494,14 +24473,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>83</v>
+        <v>582</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24523,16 +24502,16 @@
         <v>171</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>686</v>
+        <v>722</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>687</v>
+        <v>723</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>83</v>
@@ -24557,13 +24536,13 @@
         <v>83</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>507</v>
+        <v>576</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>688</v>
+        <v>586</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>689</v>
+        <v>587</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -24581,7 +24560,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24599,27 +24578,27 @@
         <v>83</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>681</v>
+        <v>588</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>682</v>
+        <v>589</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>83</v>
+        <v>591</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24630,7 +24609,7 @@
         <v>81</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>83</v>
@@ -24642,17 +24621,19 @@
         <v>83</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>691</v>
+        <v>84</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>692</v>
+        <v>725</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="N184" s="2"/>
+        <v>726</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>727</v>
+      </c>
       <c r="O184" t="s" s="2">
-        <v>694</v>
+        <v>728</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>83</v>
@@ -24701,13 +24682,13 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>83</v>
@@ -24722,1465 +24703,15 @@
         <v>83</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>83</v>
+        <v>638</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>695</v>
+        <v>639</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N185" s="2"/>
-      <c r="O185" s="2"/>
-      <c r="P185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AO185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP185" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O186" s="2"/>
-      <c r="P186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP186" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O187" s="2"/>
-      <c r="P187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP188" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP189" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP190" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP191" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP193" t="s" s="2">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP194" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="P195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP195" t="s" s="2">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="P196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP196" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7035" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7035" uniqueCount="731">
   <si>
     <t>Property</t>
   </si>
@@ -1058,6 +1058,9 @@
     <t>root</t>
   </si>
   <si>
+    <t>特定の歯の『歯根』を指定</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalRootBodyStructure_VS</t>
   </si>
   <si>
@@ -1110,6 +1113,9 @@
   </si>
   <si>
     <t>surface</t>
+  </si>
+  <si>
+    <t>特定の歯の『歯面』を指定</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
@@ -11716,10 +11722,10 @@
         <v>186</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>187</v>
+        <v>339</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>189</v>
@@ -11754,7 +11760,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11807,10 +11813,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11925,10 +11931,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12045,10 +12051,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12090,7 +12096,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -12167,10 +12173,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12287,10 +12293,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12407,10 +12413,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12527,10 +12533,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12649,13 +12655,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>335</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>83</v>
@@ -12680,10 +12686,10 @@
         <v>186</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>187</v>
+        <v>358</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>189</v>
@@ -12718,7 +12724,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12771,10 +12777,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12889,10 +12895,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13009,10 +13015,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13054,7 +13060,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>83</v>
@@ -13131,10 +13137,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13251,10 +13257,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13371,10 +13377,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13491,10 +13497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13613,10 +13619,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13735,7 +13741,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>163</v>
@@ -13778,7 +13784,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>83</v>
@@ -13855,7 +13861,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>170</v>
@@ -13973,10 +13979,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14002,16 +14008,16 @@
         <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14060,7 +14066,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14095,10 +14101,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14121,19 +14127,19 @@
         <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14182,7 +14188,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14197,19 +14203,19 @@
         <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -14217,14 +14223,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14243,19 +14249,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14304,7 +14310,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14319,16 +14325,16 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14339,14 +14345,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14365,16 +14371,16 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14424,7 +14430,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14439,16 +14445,16 @@
         <v>106</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14459,10 +14465,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14488,16 +14494,16 @@
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14525,10 +14531,10 @@
         <v>269</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14546,7 +14552,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14561,19 +14567,19 @@
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14581,10 +14587,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14592,7 +14598,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>82</v>
@@ -14610,16 +14616,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14647,16 +14653,16 @@
         <v>118</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AC101" s="2"/>
       <c r="AD101" t="s" s="2">
@@ -14666,7 +14672,7 @@
         <v>143</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14690,10 +14696,10 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
@@ -14701,13 +14707,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>83</v>
@@ -14732,16 +14738,16 @@
         <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14770,7 +14776,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14788,7 +14794,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14812,10 +14818,10 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -14823,10 +14829,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14941,10 +14947,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15061,10 +15067,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15183,10 +15189,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15301,10 +15307,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15421,10 +15427,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15466,7 +15472,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>83</v>
@@ -15543,10 +15549,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15663,10 +15669,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15706,7 +15712,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>83</v>
@@ -15783,10 +15789,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15903,10 +15909,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16025,10 +16031,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16147,13 +16153,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16178,16 +16184,16 @@
         <v>171</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16215,10 +16221,10 @@
         <v>118</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16236,7 +16242,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16260,10 +16266,10 @@
         <v>83</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16271,10 +16277,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16389,10 +16395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16509,10 +16515,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16631,10 +16637,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16749,10 +16755,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16869,10 +16875,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16914,7 +16920,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>83</v>
@@ -16991,10 +16997,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17111,10 +17117,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17154,7 +17160,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -17231,10 +17237,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17351,10 +17357,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17473,10 +17479,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17595,13 +17601,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>83</v>
@@ -17626,16 +17632,16 @@
         <v>171</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
@@ -17664,7 +17670,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>83</v>
@@ -17682,7 +17688,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17706,10 +17712,10 @@
         <v>83</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>83</v>
@@ -17717,10 +17723,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17835,10 +17841,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17955,10 +17961,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18077,10 +18083,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18195,10 +18201,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18315,10 +18321,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18360,7 +18366,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>83</v>
@@ -18437,10 +18443,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18557,10 +18563,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18600,7 +18606,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>83</v>
@@ -18677,10 +18683,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18797,10 +18803,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18919,10 +18925,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19041,14 +19047,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19070,16 +19076,16 @@
         <v>171</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
@@ -19104,13 +19110,13 @@
         <v>83</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>83</v>
@@ -19128,7 +19134,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>94</v>
@@ -19143,30 +19149,30 @@
         <v>106</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19281,10 +19287,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19401,10 +19407,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19430,10 +19436,10 @@
         <v>186</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>189</v>
@@ -19523,10 +19529,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19641,10 +19647,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19761,10 +19767,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19806,7 +19812,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>83</v>
@@ -19883,10 +19889,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20003,10 +20009,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20046,7 +20052,7 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>83</v>
@@ -20123,10 +20129,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20169,7 +20175,7 @@
         <v>83</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>83</v>
@@ -20243,10 +20249,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20365,10 +20371,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20487,10 +20493,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20513,19 +20519,19 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20574,7 +20580,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20589,19 +20595,19 @@
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>83</v>
@@ -20609,10 +20615,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20635,16 +20641,16 @@
         <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20694,7 +20700,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20715,13 +20721,13 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AP151" t="s" s="2">
         <v>83</v>
@@ -20729,14 +20735,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20755,19 +20761,19 @@
         <v>95</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
@@ -20816,7 +20822,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20831,19 +20837,19 @@
         <v>106</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AP152" t="s" s="2">
         <v>83</v>
@@ -20851,14 +20857,14 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -20877,19 +20883,19 @@
         <v>95</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>83</v>
@@ -20938,7 +20944,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -20953,19 +20959,19 @@
         <v>106</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AP153" t="s" s="2">
         <v>83</v>
@@ -20973,10 +20979,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20999,16 +21005,16 @@
         <v>95</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21058,7 +21064,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21079,13 +21085,13 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AP154" t="s" s="2">
         <v>83</v>
@@ -21093,10 +21099,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21119,19 +21125,19 @@
         <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21180,7 +21186,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21195,19 +21201,19 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AP155" t="s" s="2">
         <v>83</v>
@@ -21215,10 +21221,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21244,16 +21250,16 @@
         <v>171</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -21302,7 +21308,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21311,7 +21317,7 @@
         <v>94</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>106</v>
@@ -21320,10 +21326,10 @@
         <v>83</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>302</v>
@@ -21332,15 +21338,15 @@
         <v>83</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21366,16 +21372,16 @@
         <v>171</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -21400,13 +21406,13 @@
         <v>83</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>83</v>
@@ -21424,7 +21430,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21433,7 +21439,7 @@
         <v>94</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>106</v>
@@ -21448,7 +21454,7 @@
         <v>137</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21459,14 +21465,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21488,16 +21494,16 @@
         <v>171</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>83</v>
@@ -21522,13 +21528,13 @@
         <v>83</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>83</v>
@@ -21546,7 +21552,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21564,27 +21570,27 @@
         <v>83</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21607,19 +21613,19 @@
         <v>83</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
@@ -21668,7 +21674,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -21689,10 +21695,10 @@
         <v>83</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>83</v>
@@ -21703,10 +21709,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21732,13 +21738,13 @@
         <v>171</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21764,13 +21770,13 @@
         <v>83</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>83</v>
@@ -21788,7 +21794,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21806,27 +21812,27 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21852,16 +21858,16 @@
         <v>171</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -21886,13 +21892,13 @@
         <v>83</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>83</v>
@@ -21910,7 +21916,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -21931,10 +21937,10 @@
         <v>83</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>83</v>
@@ -21945,10 +21951,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21971,16 +21977,16 @@
         <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22030,7 +22036,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22048,27 +22054,27 @@
         <v>83</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22091,16 +22097,16 @@
         <v>83</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22150,7 +22156,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22168,27 +22174,27 @@
         <v>83</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22211,19 +22217,19 @@
         <v>83</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>83</v>
@@ -22272,7 +22278,7 @@
         <v>83</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -22284,7 +22290,7 @@
         <v>83</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>83</v>
@@ -22293,10 +22299,10 @@
         <v>83</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>83</v>
@@ -22307,10 +22313,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22425,10 +22431,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22545,14 +22551,14 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22574,16 +22580,16 @@
         <v>139</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>83</v>
@@ -22632,7 +22638,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22667,10 +22673,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22693,13 +22699,13 @@
         <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22750,7 +22756,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22759,7 +22765,7 @@
         <v>94</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>106</v>
@@ -22771,10 +22777,10 @@
         <v>83</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
@@ -22785,10 +22791,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22811,13 +22817,13 @@
         <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22868,7 +22874,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -22877,7 +22883,7 @@
         <v>94</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>106</v>
@@ -22889,10 +22895,10 @@
         <v>83</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -22903,10 +22909,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22932,16 +22938,16 @@
         <v>171</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>83</v>
@@ -22969,10 +22975,10 @@
         <v>118</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>83</v>
@@ -22990,7 +22996,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23008,13 +23014,13 @@
         <v>83</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -23025,10 +23031,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23054,16 +23060,16 @@
         <v>171</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>83</v>
@@ -23088,13 +23094,13 @@
         <v>83</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>83</v>
@@ -23112,7 +23118,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23130,13 +23136,13 @@
         <v>83</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>83</v>
@@ -23147,10 +23153,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23173,17 +23179,17 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>83</v>
@@ -23232,7 +23238,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23256,7 +23262,7 @@
         <v>83</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>83</v>
@@ -23267,10 +23273,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23296,10 +23302,10 @@
         <v>153</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23350,7 +23356,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -23371,10 +23377,10 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -23385,10 +23391,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23411,16 +23417,16 @@
         <v>95</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23470,7 +23476,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -23491,10 +23497,10 @@
         <v>83</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>83</v>
@@ -23505,10 +23511,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23531,16 +23537,16 @@
         <v>95</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23590,7 +23596,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23611,10 +23617,10 @@
         <v>83</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>83</v>
@@ -23625,10 +23631,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23651,19 +23657,19 @@
         <v>95</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>83</v>
@@ -23712,7 +23718,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -23733,10 +23739,10 @@
         <v>83</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>83</v>
@@ -23747,10 +23753,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23865,10 +23871,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23985,14 +23991,14 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -24014,16 +24020,16 @@
         <v>139</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>183</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>83</v>
@@ -24072,7 +24078,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24107,10 +24113,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24136,16 +24142,16 @@
         <v>171</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>83</v>
@@ -24170,13 +24176,13 @@
         <v>83</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>83</v>
@@ -24194,7 +24200,7 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>94</v>
@@ -24212,16 +24218,16 @@
         <v>83</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>83</v>
@@ -24229,10 +24235,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24255,19 +24261,19 @@
         <v>95</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>83</v>
@@ -24316,7 +24322,7 @@
         <v>83</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24334,10 +24340,10 @@
         <v>83</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>302</v>
@@ -24346,15 +24352,15 @@
         <v>83</v>
       </c>
       <c r="AP181" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24380,16 +24386,16 @@
         <v>171</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>83</v>
@@ -24414,13 +24420,13 @@
         <v>83</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>83</v>
@@ -24438,7 +24444,7 @@
         <v>83</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24447,7 +24453,7 @@
         <v>94</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>106</v>
@@ -24462,7 +24468,7 @@
         <v>137</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>83</v>
@@ -24473,14 +24479,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24502,16 +24508,16 @@
         <v>171</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>83</v>
@@ -24536,13 +24542,13 @@
         <v>83</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>83</v>
@@ -24560,7 +24566,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24578,27 +24584,27 @@
         <v>83</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24624,16 +24630,16 @@
         <v>84</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>83</v>
@@ -24682,7 +24688,7 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -24703,10 +24709,10 @@
         <v>83</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>83</v>
